--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
@@ -536,28 +536,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -568,28 +568,28 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>42</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -603,28 +603,28 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>9.1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -635,28 +635,28 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>9.1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -731,28 +731,28 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>82</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>93.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -852,13 +852,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -884,13 +884,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -919,13 +919,13 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -951,13 +951,13 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1047,13 +1047,13 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1168,28 +1168,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1200,28 +1200,28 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>42</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1235,28 +1235,28 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>9.1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1267,28 +1267,28 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>9.1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1363,28 +1363,28 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>82</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>93.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
@@ -820,25 +820,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -855,25 +855,25 @@
         <v>12</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -887,25 +887,25 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -922,25 +922,25 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -954,25 +954,25 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -989,25 +989,25 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1021,25 +1021,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1050,25 +1050,25 @@
         <v>84</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>2.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
@@ -536,22 +536,22 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -568,22 +568,22 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>42</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -603,10 +603,10 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -635,10 +635,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -650,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -731,22 +731,22 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>97.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="H9" s="1">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -852,22 +852,22 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -884,22 +884,22 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>42</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -919,10 +919,10 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -951,10 +951,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1047,22 +1047,22 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>97.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="H9" s="1">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1168,22 +1168,22 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1200,22 +1200,22 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>42</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1235,10 +1235,10 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1363,22 +1363,22 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>97.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="H9" s="1">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1171,19 +1171,19 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>7.7</v>
-      </c>
-      <c r="I3" s="2">
-        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1203,19 +1203,19 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1305,19 +1305,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1337,19 +1337,19 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1366,16 +1366,16 @@
         <v>86</v>
       </c>
       <c r="E9">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>8.4</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20231.xlsx
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
